--- a/src/vo_new_terms_IDs.xlsx
+++ b/src/vo_new_terms_IDs.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiezhen/Documents/Ontology/VO/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAC9EF3-80AA-8048-9ABC-3D68CEC2CCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479FC3A5-F191-CD4B-BBA2-5BF7E2B1F186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10240" yWindow="2060" windowWidth="20680" windowHeight="13000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6120" yWindow="1860" windowWidth="20680" windowHeight="13000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VO IDs range" sheetId="2" r:id="rId1"/>
+    <sheet name="new terms with IDs" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="528">
   <si>
     <t>vaccine adjuvant</t>
   </si>
@@ -86,15 +87,6 @@
     <t>VO:0021181</t>
   </si>
   <si>
-    <t>ID assigned to ajuvants that will be added to VO</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/spreadsheets/d/1HelnswxZv1ConGKWusuEO6XzDLe9hjEog1ejSiVOQhs/edit?gid=1705240071#gid=1705240071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detail see: </t>
-  </si>
-  <si>
     <t>TLR agonist vaccine adjuvant</t>
   </si>
   <si>
@@ -821,9 +813,6 @@
     <t>VO:0005764</t>
   </si>
   <si>
-    <t>All ID changed</t>
-  </si>
-  <si>
     <t>1P7 vaccine adjuvant</t>
   </si>
   <si>
@@ -1619,7 +1608,16 @@
     <t>adenovirus-mediated vaccine adjuvant</t>
   </si>
   <si>
-    <t>VO_0005780 - VO_0005799</t>
+    <t>VO_0005781 - VO_0005799</t>
+  </si>
+  <si>
+    <t>VO:0005780</t>
+  </si>
+  <si>
+    <t>Advax4 vaccine adjuvant</t>
+  </si>
+  <si>
+    <t>ID assigned to ajuvants</t>
   </si>
 </sst>
 </file>
@@ -2071,7 +2069,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -2186,34 +2184,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2262,7 +2232,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2285,15 +2255,13 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="44" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="44"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="45">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2676,164 +2644,59 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.33203125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="19.1640625" customWidth="1"/>
-    <col min="8" max="8" width="30.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>18</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="I3" t="s">
-        <v>262</v>
-      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G5" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G6" s="20" t="s">
-        <v>474</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G7" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>266</v>
-      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>267</v>
-      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>268</v>
-      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B10" s="10"/>
       <c r="C10" s="9"/>
-      <c r="G10" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>269</v>
-      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B11" s="10"/>
       <c r="C11" s="9"/>
-      <c r="G11" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>270</v>
-      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>271</v>
-      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G14" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>273</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="G15" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" s="19" t="s">
-        <v>274</v>
-      </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
@@ -2842,2109 +2705,204 @@
       <c r="C16" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G18" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="H18" s="19" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G19" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="H19" s="19" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G20" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G21" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G24" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="H24" s="19" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G25" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="H25" s="19" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G26" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="H26" s="19" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G27" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="H27" s="19" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G28" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="H28" s="19" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G29" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="H29" s="19" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G30" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="H30" s="19" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G31" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H31" s="19" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G32" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="H32" s="19" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G33" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="H33" s="19" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34"/>
-      <c r="G34" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="H34" s="19" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35"/>
-      <c r="G35" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="H35" s="19" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36"/>
-      <c r="G36" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="H36" s="19" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37"/>
-      <c r="G37" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="H37" s="19" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38"/>
-      <c r="G38" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="H38" s="19" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39"/>
-      <c r="G39" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="H39" s="19" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40"/>
-      <c r="G40" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="H40" s="19" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41"/>
-      <c r="G41" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="H41" s="19" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42"/>
-      <c r="G42" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="H42" s="19" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43"/>
-      <c r="G43" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="H43" s="19" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44"/>
-      <c r="G44" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="H44" s="19" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45"/>
-      <c r="G45" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="H45" s="19" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46"/>
-      <c r="G46" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H46" s="19" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47"/>
-      <c r="G47" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="H47" s="19" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48"/>
-      <c r="G48" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="H48" s="19" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49"/>
-      <c r="G49" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="H49" s="19" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50"/>
-      <c r="G50" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="H50" s="19" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51"/>
-      <c r="G51" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="H51" s="19" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52"/>
-      <c r="G52" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="H52" s="19" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53"/>
-      <c r="G53" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="H53" s="19" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54"/>
-      <c r="G54" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="H54" s="19" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55"/>
-      <c r="G55" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="H55" s="19" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56"/>
-      <c r="G56" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="H56" s="19" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57"/>
-      <c r="G57" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="H57" s="19" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58"/>
-      <c r="G58" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H58" s="19" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59"/>
-      <c r="G59" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="H59" s="19" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60"/>
-      <c r="G60" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H60" s="19" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61"/>
-      <c r="G61" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="H61" s="19" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62"/>
-      <c r="G62" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="H62" s="19" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63"/>
-      <c r="G63" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="H63" s="19" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64"/>
-      <c r="G64" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="H64" s="19" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65"/>
-      <c r="G65" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="H65" s="19" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66"/>
-      <c r="G66" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="H66" s="19" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67"/>
-      <c r="G67" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="H67" s="19" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68"/>
-      <c r="G68" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="H68" s="19" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69"/>
-      <c r="G69" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="H69" s="19" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70"/>
-      <c r="G70" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="H70" s="19" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71"/>
-      <c r="G71" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="H71" s="19" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72"/>
-      <c r="G72" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="H72" s="19" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73"/>
-      <c r="G73" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="H73" s="19" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74"/>
-      <c r="G74" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="H74" s="19" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75"/>
-      <c r="G75" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="H75" s="19" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76"/>
-      <c r="G76" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="H76" s="19" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77"/>
-      <c r="G77" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="H77" s="19" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78"/>
-      <c r="G78" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="H78" s="19" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79"/>
-      <c r="G79" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="H79" s="19" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80"/>
-      <c r="G80" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="H80" s="19" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81"/>
-      <c r="G81" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="H81" s="19" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82"/>
-      <c r="G82" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="H82" s="19" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G83" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="H83" s="19" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G84" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="H84" s="19" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G85" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="H85" s="19" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G86" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="H86" s="19" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G87" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="H87" s="19" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G88" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H88" s="19" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G89" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="H89" s="19" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G90" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="H90" s="19" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G91" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="H91" s="19" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G92" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="H92" s="19" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G93" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="H93" s="19" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G94" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="H94" s="19" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G95" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="H95" s="19" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G96" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="H96" s="19" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="97" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G97" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="H97" s="19" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="98" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G98" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="H98" s="19" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="99" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G99" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="H99" s="19" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="100" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G100" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="H100" s="19" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="101" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G101" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H101" s="19" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="102" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G102" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="H102" s="19" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="103" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G103" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="H103" s="19" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="104" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G104" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="H104" s="19" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="105" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G105" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="H105" s="19" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="106" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G106" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="H106" s="19" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="107" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G107" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="H107" s="19" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="108" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G108" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="H108" s="19" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="109" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G109" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="H109" s="19" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="110" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G110" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="H110" s="19" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="111" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G111" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="H111" s="19" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="112" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G112" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="H112" s="19" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="113" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G113" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="H113" s="19" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="114" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G114" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="H114" s="19" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="115" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G115" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="H115" s="19" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="116" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G116" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="H116" s="19" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="117" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G117" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="H117" s="19" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="118" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G118" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="H118" s="19" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="119" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G119" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="H119" s="19" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="120" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G120" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="H120" s="19" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="121" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G121" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="H121" s="19" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="122" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G122" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="H122" s="19" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="123" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G123" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="H123" s="19" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="124" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G124" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="H124" s="19" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="125" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G125" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="H125" s="19" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="126" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G126" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="H126" s="19" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="127" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G127" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="H127" s="19" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="128" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G128" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="H128" s="19" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="129" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G129" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="H129" s="19" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="130" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G130" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="H130" s="19" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="131" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G131" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="H131" s="19" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="132" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G132" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="H132" s="19" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="133" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G133" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="H133" s="19" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="134" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G134" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="H134" s="19" t="s">
-        <v>392</v>
-      </c>
-      <c r="I134" s="24"/>
-    </row>
-    <row r="135" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G135" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="H135" s="19" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="136" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G136" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="H136" s="19" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="137" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G137" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="H137" s="19" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="138" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G138" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="H138" s="19" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="139" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G139" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="H139" s="19" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="140" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G140" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="H140" s="19" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="141" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G141" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="H141" s="19" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="142" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G142" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="H142" s="19" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="143" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G143" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="H143" s="19" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="144" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G144" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="H144" s="19" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="145" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G145" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="H145" s="19" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="146" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G146" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="H146" s="19" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="147" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G147" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="H147" s="19" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="148" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G148" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="H148" s="19" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="149" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G149" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="H149" s="19" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="150" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G150" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="H150" s="19" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="151" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G151" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="H151" s="19" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="152" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G152" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="H152" s="19" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="153" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G153" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="H153" s="19" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="154" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G154" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="H154" s="19" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="155" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G155" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="H155" s="19" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="156" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G156" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="H156" s="19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="157" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G157" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="H157" s="19" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="158" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G158" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="H158" s="19" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="159" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G159" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="H159" s="19" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="160" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G160" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="H160" s="19" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="161" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G161" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="H161" s="19" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="162" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G162" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="H162" s="19" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="163" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G163" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="H163" s="19" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="164" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G164" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="H164" s="19" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="165" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G165" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="H165" s="19" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="166" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G166" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="H166" s="19" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="167" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G167" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="H167" s="19" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="168" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G168" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="H168" s="19" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="169" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G169" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="H169" s="19" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="170" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G170" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="H170" s="19" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="171" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G171" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="H171" s="19" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="172" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G172" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="H172" s="19" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="173" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G173" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="H173" s="19" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="174" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G174" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="H174" s="19" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="175" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G175" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="H175" s="19" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="176" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G176" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="H176" s="19" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="177" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G177" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="H177" s="19" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="178" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G178" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="H178" s="19" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="179" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G179" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="H179" s="19" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="180" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G180" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="H180" s="19" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="181" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G181" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="H181" s="19" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="182" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G182" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="H182" s="19" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="183" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G183" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="H183" s="19" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="184" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G184" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="H184" s="19" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="185" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G185" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="H185" s="19" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="186" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G186" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="H186" s="19" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="187" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G187" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="H187" s="19" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="188" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G188" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="H188" s="19" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="189" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G189" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="H189" s="19" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="190" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G190" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="H190" s="19" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="191" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G191" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="H191" s="19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="192" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G192" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="H192" s="19" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G193" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="H193" s="19" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G194" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="H194" s="19" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G195" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="H195" s="19" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G196" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="H196" s="19" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A197" s="21"/>
-      <c r="B197" s="22"/>
-      <c r="C197" s="22"/>
-      <c r="D197" s="22"/>
-      <c r="E197" s="22"/>
-      <c r="F197" s="22"/>
-      <c r="G197" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="H197" s="19" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A198" s="21"/>
-      <c r="B198" s="22"/>
-      <c r="C198" s="22"/>
-      <c r="D198" s="22"/>
-      <c r="E198" s="22"/>
-      <c r="F198" s="22"/>
-      <c r="G198" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="H198" s="19" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A199" s="21"/>
-      <c r="B199" s="22"/>
-      <c r="C199" s="22"/>
-      <c r="D199" s="22"/>
-      <c r="E199" s="22"/>
-      <c r="F199" s="22"/>
-      <c r="G199" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="H199" s="19" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A200" s="21"/>
-      <c r="B200" s="22"/>
-      <c r="C200" s="22"/>
-      <c r="D200" s="22"/>
-      <c r="E200" s="22"/>
-      <c r="F200" s="22"/>
-      <c r="G200" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="H200" s="19" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A201" s="21"/>
-      <c r="B201" s="22"/>
-      <c r="C201" s="22"/>
-      <c r="D201" s="22"/>
-      <c r="E201" s="22"/>
-      <c r="F201" s="22"/>
-      <c r="G201" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="H201" s="19" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A202" s="21"/>
-      <c r="B202" s="22"/>
-      <c r="C202" s="22"/>
-      <c r="D202" s="22"/>
-      <c r="E202" s="22"/>
-      <c r="F202" s="22"/>
-      <c r="G202" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="H202" s="19" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A203" s="21"/>
-      <c r="B203" s="22"/>
-      <c r="C203" s="22"/>
-      <c r="D203" s="22"/>
-      <c r="E203" s="22"/>
-      <c r="F203" s="22"/>
-      <c r="G203" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="H203" s="19" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A204" s="21"/>
-      <c r="B204" s="22"/>
-      <c r="C204" s="22"/>
-      <c r="D204" s="22"/>
-      <c r="E204" s="22"/>
-      <c r="F204" s="22"/>
-      <c r="G204" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="H204" s="19" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A205" s="21"/>
-      <c r="B205" s="22"/>
-      <c r="C205" s="22"/>
-      <c r="D205" s="22"/>
-      <c r="E205" s="22"/>
-      <c r="F205" s="22"/>
-      <c r="G205" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="H205" s="19" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A206" s="21"/>
-      <c r="B206" s="22"/>
-      <c r="C206" s="22"/>
-      <c r="D206" s="22"/>
-      <c r="E206" s="22"/>
-      <c r="F206" s="22"/>
-      <c r="G206" s="18" t="s">
-        <v>228</v>
-      </c>
-      <c r="H206" s="19" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A207" s="21"/>
-      <c r="B207" s="22"/>
-      <c r="C207" s="22"/>
-      <c r="D207" s="22"/>
-      <c r="E207" s="22"/>
-      <c r="F207" s="22"/>
-      <c r="G207" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="H207" s="19" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A208" s="21"/>
-      <c r="B208" s="22"/>
-      <c r="C208" s="22"/>
-      <c r="D208" s="23"/>
-      <c r="E208" s="22"/>
-      <c r="F208" s="22"/>
-      <c r="G208" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="H208" s="19" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A209" s="21"/>
-      <c r="B209" s="22"/>
-      <c r="C209" s="22"/>
-      <c r="D209" s="22"/>
-      <c r="E209" s="22"/>
-      <c r="F209" s="22"/>
-      <c r="G209" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="H209" s="19" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A210" s="21"/>
-      <c r="B210" s="22"/>
-      <c r="C210" s="22"/>
-      <c r="D210" s="22"/>
-      <c r="E210" s="22"/>
-      <c r="F210" s="22"/>
-      <c r="G210" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="H210" s="19" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A211" s="21"/>
-      <c r="B211" s="22"/>
-      <c r="C211" s="22"/>
-      <c r="D211" s="22"/>
-      <c r="E211" s="22"/>
-      <c r="F211" s="22"/>
-      <c r="G211" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="H211" s="19" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A212" s="21"/>
-      <c r="B212" s="22"/>
-      <c r="C212" s="22"/>
-      <c r="D212" s="22"/>
-      <c r="E212" s="22"/>
-      <c r="F212" s="22"/>
-      <c r="G212" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="H212" s="19" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G213" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="H213" s="19" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G214" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="H214" s="19" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G215" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="H215" s="19" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G216" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="H216" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G217" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="H217" s="19" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G218" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="H218" s="19" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G219" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="H219" s="19" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G220" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="H220" s="19" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G221" s="20" t="s">
-        <v>243</v>
-      </c>
-      <c r="H221" s="19" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G222" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="H222" s="19" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G223" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="H223" s="19" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G224" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="H224" s="19" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="225" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G225" s="20" t="s">
-        <v>247</v>
-      </c>
-      <c r="H225" s="19" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="226" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G226" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="H226" s="25" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="227" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G227" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="H227" s="25" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="228" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G228" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="H228" s="25" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="229" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G229" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="H229" s="25" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="230" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G230" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="H230" s="25" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="231" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G231" s="20" t="s">
-        <v>253</v>
-      </c>
-      <c r="H231" s="25" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="232" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G232" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="H232" s="25" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="233" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G233" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="H233" s="25" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="234" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G234" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="H234" s="25" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="235" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G235" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="H235" s="25" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="236" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G236" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="H236" s="25" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="237" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G237" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="H237" s="25" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="238" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G238" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="H238" s="25" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="239" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G239" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="H239" s="25" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="240" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G240" s="20" t="s">
-        <v>484</v>
-      </c>
-      <c r="H240" s="25" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="241" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G241" s="20" t="s">
-        <v>485</v>
-      </c>
-      <c r="H241" s="25" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="242" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G242" s="20" t="s">
-        <v>486</v>
-      </c>
-      <c r="H242" s="25" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="243" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G243" s="20" t="s">
-        <v>487</v>
-      </c>
-      <c r="H243" s="25" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="244" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G244" s="20" t="s">
-        <v>488</v>
-      </c>
-      <c r="H244" s="25" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="245" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G245" s="20" t="s">
-        <v>489</v>
-      </c>
-      <c r="H245" s="25" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="246" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G246" s="20" t="s">
-        <v>490</v>
-      </c>
-      <c r="H246" s="25" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="247" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G247" s="20" t="s">
-        <v>491</v>
-      </c>
-      <c r="H247" s="25" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="248" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G248" s="20" t="s">
-        <v>492</v>
-      </c>
-      <c r="H248" s="25" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="249" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G249" s="20" t="s">
-        <v>493</v>
-      </c>
-      <c r="H249" s="25" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="250" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G250" s="20" t="s">
-        <v>494</v>
-      </c>
-      <c r="H250" s="26" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="251" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G251" t="s">
-        <v>495</v>
-      </c>
-      <c r="H251" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="252" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G252" t="s">
-        <v>496</v>
-      </c>
-      <c r="H252" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="253" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G253" t="s">
-        <v>524</v>
-      </c>
-      <c r="H253" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="254" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G254" t="s">
-        <v>526</v>
-      </c>
-      <c r="H254" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="255" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G255" s="1"/>
-    </row>
-    <row r="256" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G256" s="1"/>
-    </row>
-    <row r="257" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G257" s="1"/>
+    </row>
+    <row r="208" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D208" s="18"/>
+    </row>
+    <row r="257" spans="9:9" x14ac:dyDescent="0.2">
       <c r="I257" s="15"/>
     </row>
-    <row r="258" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G258" s="1"/>
+    <row r="258" spans="9:9" x14ac:dyDescent="0.2">
       <c r="I258" s="16"/>
     </row>
-    <row r="259" spans="7:9" x14ac:dyDescent="0.2">
-      <c r="G259" s="1"/>
+    <row r="259" spans="9:9" x14ac:dyDescent="0.2">
       <c r="I259" s="17"/>
     </row>
-    <row r="260" spans="7:9" x14ac:dyDescent="0.2">
+    <row r="260" spans="9:9" x14ac:dyDescent="0.2">
       <c r="I260" s="17"/>
     </row>
     <row r="5455" spans="1:1" x14ac:dyDescent="0.2">
@@ -4961,10 +2919,2070 @@
     <sortCondition ref="G1:G5525"/>
   </sortState>
   <phoneticPr fontId="21" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" location="gid=1705240071" xr:uid="{9A45402F-F49A-7A46-9FDB-BC4722C03E51}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382F4F77-36EB-FB4D-9816-70F16A92F51F}">
+  <dimension ref="A1:B259"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.33203125" style="19" customWidth="1"/>
+    <col min="2" max="2" width="30.1640625" style="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="24" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="21" t="s">
+        <v>470</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B61" s="21" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B66" s="21" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B68" s="21" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B69" s="21" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B70" s="21" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B71" s="21" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B72" s="21" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B73" s="21" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B74" s="21" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B75" s="21" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B76" s="21" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B77" s="21" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B78" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B79" s="21" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B80" s="21" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B81" s="21" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B82" s="21" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B83" s="21" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B84" s="21" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B85" s="21" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="B86" s="21" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B87" s="21" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B88" s="21" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B89" s="21" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B90" s="21" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B91" s="21" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B92" s="21" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="B93" s="21" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B94" s="21" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B95" s="21" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B96" s="21" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B97" s="21" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B98" s="21" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B99" s="21" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B100" s="21" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B101" s="21" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B102" s="21" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B103" s="21" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B104" s="21" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B105" s="21" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B106" s="21" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B107" s="21" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B108" s="21" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B109" s="21" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B110" s="21" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B111" s="21" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B112" s="21" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B113" s="21" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B114" s="21" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B115" s="21" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="B116" s="21" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B117" s="21" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B118" s="21" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B119" s="21" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B120" s="21" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B121" s="21" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B122" s="21" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="B123" s="21" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="B124" s="21" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B125" s="21" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="B126" s="21" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B127" s="21" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="B128" s="21" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B129" s="21" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="B130" s="21" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B131" s="21" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B132" s="21" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B133" s="21" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="B134" s="21" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="B135" s="21" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="B136" s="21" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B137" s="21" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="B138" s="21" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="B139" s="21" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="B140" s="21" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B141" s="21" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="B142" s="21" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="B143" s="21" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B144" s="21" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B145" s="21" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B146" s="21" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="B147" s="21" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="B148" s="21" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="B149" s="21" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="B150" s="21" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="B151" s="21" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="B152" s="21" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="B153" s="21" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="B154" s="21" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="B155" s="21" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="B156" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="B157" s="21" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="B158" s="21" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="B159" s="21" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A160" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="B160" s="21" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B161" s="21" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="B162" s="21" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="B163" s="21" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="B164" s="21" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="B165" s="21" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="B166" s="21" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="B167" s="21" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="B168" s="21" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="B169" s="21" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A170" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="B170" s="21" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A171" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B171" s="21" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A172" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="B172" s="21" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A173" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="B173" s="21" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A174" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B174" s="21" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A175" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="B175" s="21" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A176" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="B176" s="21" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A177" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="B177" s="21" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A178" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="B178" s="21" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A179" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="B179" s="21" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A180" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="B180" s="21" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A181" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="B181" s="21" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A182" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="B182" s="21" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A183" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="B183" s="21" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A184" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="B184" s="21" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A185" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="B185" s="21" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A186" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="B186" s="21" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A187" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="B187" s="21" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A188" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="B188" s="21" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A189" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="B189" s="21" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A190" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="B190" s="21" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A191" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="B191" s="21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A192" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="B192" s="21" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A193" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="B193" s="21" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A194" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="B194" s="21" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A195" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="B195" s="21" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A196" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="B196" s="21" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A197" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="B197" s="21" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A198" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="B198" s="21" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A199" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="B199" s="21" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A200" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="B200" s="21" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A201" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="B201" s="21" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A202" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="B202" s="21" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A203" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="B203" s="21" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A204" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="B204" s="21" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A205" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="B205" s="21" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A206" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="B206" s="21" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A207" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="B207" s="21" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A208" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="B208" s="21" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A209" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="B209" s="21" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A210" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="B210" s="21" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A211" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B211" s="21" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A212" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="B212" s="21" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A213" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="B213" s="21" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A214" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="B214" s="21" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A215" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="B215" s="21" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A216" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="B216" s="21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A217" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="B217" s="21" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A218" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="B218" s="21" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A219" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="B219" s="21" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A220" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="B220" s="21" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A221" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="B221" s="21" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A222" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="B222" s="21" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A223" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="B223" s="21" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A224" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="B224" s="21" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A225" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="B225" s="21" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A226" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="B226" s="22" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A227" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="B227" s="22" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A228" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="B228" s="22" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A229" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="B229" s="22" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A230" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="B230" s="22" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A231" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="B231" s="22" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A232" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B232" s="22" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A233" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="B233" s="22" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A234" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="B234" s="22" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A235" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="B235" s="22" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A236" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="B236" s="22" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A237" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="B237" s="22" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A238" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="B238" s="22" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A239" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="B239" s="22" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A240" s="21" t="s">
+        <v>480</v>
+      </c>
+      <c r="B240" s="22" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A241" s="21" t="s">
+        <v>481</v>
+      </c>
+      <c r="B241" s="22" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A242" s="21" t="s">
+        <v>482</v>
+      </c>
+      <c r="B242" s="22" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A243" s="21" t="s">
+        <v>483</v>
+      </c>
+      <c r="B243" s="22" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A244" s="21" t="s">
+        <v>484</v>
+      </c>
+      <c r="B244" s="22" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A245" s="21" t="s">
+        <v>485</v>
+      </c>
+      <c r="B245" s="22" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A246" s="21" t="s">
+        <v>486</v>
+      </c>
+      <c r="B246" s="22" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A247" s="21" t="s">
+        <v>487</v>
+      </c>
+      <c r="B247" s="22" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A248" s="21" t="s">
+        <v>488</v>
+      </c>
+      <c r="B248" s="22" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A249" s="21" t="s">
+        <v>489</v>
+      </c>
+      <c r="B249" s="22" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A250" s="21" t="s">
+        <v>490</v>
+      </c>
+      <c r="B250" s="22" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A251" s="19" t="s">
+        <v>491</v>
+      </c>
+      <c r="B251" s="19" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A252" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="B252" s="19" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A253" s="19" t="s">
+        <v>520</v>
+      </c>
+      <c r="B253" s="19" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A254" s="19" t="s">
+        <v>522</v>
+      </c>
+      <c r="B254" s="19" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A255" s="19" t="s">
+        <v>525</v>
+      </c>
+      <c r="B255" s="19" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A256" s="23"/>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A257" s="23"/>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A258" s="23"/>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A259" s="23"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/vo_new_terms_IDs.xlsx
+++ b/src/vo_new_terms_IDs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiezhen/Documents/Ontology/VO/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479FC3A5-F191-CD4B-BBA2-5BF7E2B1F186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7548C8-FA63-5248-8E5F-889599887203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6120" yWindow="1860" windowWidth="20680" windowHeight="13000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9480" yWindow="1760" windowWidth="20680" windowHeight="13000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VO IDs range" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="531">
   <si>
     <t>vaccine adjuvant</t>
   </si>
@@ -1618,13 +1618,22 @@
   </si>
   <si>
     <t>ID assigned to ajuvants</t>
+  </si>
+  <si>
+    <t>immune signature</t>
+  </si>
+  <si>
+    <t>Other kinds new terms</t>
+  </si>
+  <si>
+    <t>VO:0010504</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1862,6 +1871,12 @@
       <name val="Aptos Display"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="37">
@@ -2232,7 +2247,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2262,6 +2277,9 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="45">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2692,7 +2710,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
-        <v>21</v>
+        <v>530</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
@@ -2926,27 +2944,37 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382F4F77-36EB-FB4D-9816-70F16A92F51F}">
-  <dimension ref="A1:B259"/>
+  <dimension ref="A1:F259"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.33203125" style="19" customWidth="1"/>
     <col min="2" max="2" width="30.1640625" style="19" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E2" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="21" t="s">
         <v>23</v>
       </c>
@@ -2954,7 +2982,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
         <v>24</v>
       </c>
@@ -2962,7 +2990,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="21" t="s">
         <v>25</v>
       </c>
@@ -2970,7 +2998,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="21" t="s">
         <v>470</v>
       </c>
@@ -2978,7 +3006,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="20" t="s">
         <v>26</v>
       </c>
@@ -2986,7 +3014,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="21" t="s">
         <v>27</v>
       </c>
@@ -2994,7 +3022,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="20" t="s">
         <v>28</v>
       </c>
@@ -3002,7 +3030,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>29</v>
       </c>
@@ -3010,7 +3038,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="20" t="s">
         <v>30</v>
       </c>
@@ -3018,7 +3046,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="20" t="s">
         <v>31</v>
       </c>
@@ -3026,7 +3054,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>32</v>
       </c>
@@ -3034,7 +3062,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="20" t="s">
         <v>33</v>
       </c>
@@ -3042,7 +3070,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="20" t="s">
         <v>34</v>
       </c>
@@ -3050,7 +3078,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="21" t="s">
         <v>35</v>
       </c>

--- a/src/vo_new_terms_IDs.xlsx
+++ b/src/vo_new_terms_IDs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiezhen/Documents/Ontology/VO/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7548C8-FA63-5248-8E5F-889599887203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FD4CAA-3AF0-7F4F-B386-908C6F8984FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9480" yWindow="1760" windowWidth="20680" windowHeight="13000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6200" yWindow="2360" windowWidth="24200" windowHeight="13000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VO IDs range" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="539">
   <si>
     <t>vaccine adjuvant</t>
   </si>
@@ -48,9 +48,6 @@
     <t>New RxNorm terms</t>
   </si>
   <si>
-    <t>Assign new ID for new VO terms</t>
-  </si>
-  <si>
     <t>VO:0015001</t>
   </si>
   <si>
@@ -1627,6 +1624,33 @@
   </si>
   <si>
     <t>VO:0010504</t>
+  </si>
+  <si>
+    <t>Assign new ID for new VO classes</t>
+  </si>
+  <si>
+    <t>Assign new ID for new VO annotation or object properties</t>
+  </si>
+  <si>
+    <t>VO:1000002</t>
+  </si>
+  <si>
+    <t>annot/object properties</t>
+  </si>
+  <si>
+    <t>vaccine antigen processing and presentation</t>
+  </si>
+  <si>
+    <t>VO:0010505</t>
+  </si>
+  <si>
+    <t>dendritic cell vaccine antigen processing and presentation</t>
+  </si>
+  <si>
+    <t>VO:0010506</t>
+  </si>
+  <si>
+    <t>macrophage vaccine antigen processing and presentation</t>
   </si>
 </sst>
 </file>
@@ -2247,7 +2271,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2271,15 +2295,16 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="44"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="45">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2658,7 +2683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I5526"/>
+  <dimension ref="A1:I5529"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.33203125" style="3" customWidth="1"/>
@@ -2671,7 +2696,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I2" s="14"/>
     </row>
@@ -2687,12 +2712,12 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -2705,70 +2730,71 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>4</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
+        <v>529</v>
+      </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="13" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="9" t="s">
+      <c r="B24" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="10" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B26" s="9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36"/>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37"/>
@@ -2908,33 +2934,42 @@
     <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82"/>
     </row>
-    <row r="208" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D208" s="18"/>
-    </row>
-    <row r="257" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I257" s="15"/>
-    </row>
-    <row r="258" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I258" s="16"/>
-    </row>
-    <row r="259" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I259" s="17"/>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A83"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A84"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A85"/>
+    </row>
+    <row r="211" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D211" s="18"/>
     </row>
     <row r="260" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I260" s="17"/>
-    </row>
-    <row r="5455" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5455" s="4"/>
-    </row>
-    <row r="5513" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5513" s="6"/>
-    </row>
-    <row r="5526" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5526" s="5"/>
+      <c r="I260" s="15"/>
+    </row>
+    <row r="261" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I261" s="16"/>
+    </row>
+    <row r="262" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I262" s="17"/>
+    </row>
+    <row r="263" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I263" s="17"/>
+    </row>
+    <row r="5458" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5458" s="4"/>
+    </row>
+    <row r="5516" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5516" s="6"/>
+    </row>
+    <row r="5529" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5529" s="5"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G1:G5525">
-    <sortCondition ref="G1:G5525"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G1:G5528">
+    <sortCondition ref="G1:G5528"/>
   </sortState>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2944,2071 +2979,2093 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382F4F77-36EB-FB4D-9816-70F16A92F51F}">
-  <dimension ref="A1:F259"/>
+  <dimension ref="A1:H259"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" style="19" customWidth="1"/>
-    <col min="2" max="2" width="30.1640625" style="19" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="30.1640625" customWidth="1"/>
     <col min="5" max="5" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>526</v>
+      </c>
+      <c r="E1" t="s">
+        <v>528</v>
+      </c>
+      <c r="H1" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
         <v>527</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H2" s="23"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="E3" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="21" t="s">
+      <c r="F3" s="24" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="E4" t="s">
+        <v>535</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="E5" t="s">
+        <v>537</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="20" t="s">
+        <v>469</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B53" s="20" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B58" s="20" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B66" s="20" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B68" s="20" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B70" s="20" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B71" s="20" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B74" s="20" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B76" s="20" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B77" s="20" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B78" s="20" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B79" s="20" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B80" s="20" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B81" s="20" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B82" s="20" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B83" s="20" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B84" s="20" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B85" s="20" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B86" s="20" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B87" s="20" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B88" s="20" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B89" s="20" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B90" s="20" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B91" s="20" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B92" s="20" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B93" s="20" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B94" s="20" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B95" s="20" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B96" s="20" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B97" s="20" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B98" s="20" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B99" s="20" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B100" s="20" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="B101" s="20" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="B102" s="20" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="B103" s="20" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B104" s="20" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B105" s="20" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B106" s="20" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B107" s="20" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="B108" s="20" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B109" s="20" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="B110" s="20" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B111" s="20" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B112" s="20" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B113" s="20" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="B114" s="20" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B115" s="20" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="B116" s="20" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B117" s="20" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B118" s="20" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B119" s="20" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B120" s="20" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="B121" s="20" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="B122" s="20" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="B123" s="20" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="B124" s="20" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="B125" s="20" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="B126" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="B127" s="20" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="B128" s="20" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B129" s="20" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B130" s="20" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B131" s="20" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B132" s="20" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="B133" s="20" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="B134" s="20" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="B135" s="20" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="B136" s="20" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="B137" s="20" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="B138" s="20" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="B139" s="20" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="B140" s="20" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="B141" s="20" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="B142" s="20" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="B143" s="20" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B144" s="20" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="B145" s="20" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="B146" s="20" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B147" s="20" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="B148" s="20" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="B149" s="20" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="B150" s="20" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="B151" s="20" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="B152" s="20" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="B153" s="20" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="B154" s="20" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="B155" s="20" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="B156" s="20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="B157" s="20" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="B158" s="20" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="B159" s="20" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A160" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="B160" s="20" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="B161" s="20" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="B162" s="20" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="B163" s="20" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="B164" s="20" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="B165" s="20" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="B166" s="20" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="B167" s="20" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="B168" s="20" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="B169" s="20" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A170" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="B170" s="20" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A171" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="B171" s="20" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A172" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="B172" s="20" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A173" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="B173" s="20" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A174" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="B174" s="20" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A175" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="B175" s="20" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A176" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="B176" s="20" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A177" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="B177" s="20" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A178" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="B178" s="20" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A179" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="B179" s="20" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A180" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="B180" s="20" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A181" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="B181" s="20" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A182" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="B182" s="20" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A183" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="B183" s="20" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A184" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="B184" s="20" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A185" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="B185" s="20" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A186" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="B186" s="20" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A187" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="B187" s="20" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A188" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="B188" s="20" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A189" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="B189" s="20" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A190" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="B190" s="20" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A191" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="B191" s="20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A192" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="B192" s="20" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A193" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="B193" s="20" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A194" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="B194" s="20" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A195" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="B195" s="20" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A196" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B196" s="20" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A197" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B197" s="20" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A198" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="B198" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A199" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="B199" s="20" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A200" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="B200" s="20" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A201" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="B201" s="20" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A202" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="B202" s="20" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A203" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B203" s="20" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A204" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="B204" s="20" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A205" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="B205" s="20" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A206" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="B206" s="20" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A207" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B207" s="20" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A208" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="B208" s="20" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A209" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="B209" s="20" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A210" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="B210" s="20" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A211" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="B211" s="20" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A212" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="B212" s="20" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A213" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="B213" s="20" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A214" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="B214" s="20" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A215" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="B215" s="20" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A216" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="B216" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="21" t="s">
-        <v>470</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="21" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="21" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="21" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="21" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="21" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" s="21" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" s="21" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" s="21" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32" s="21" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="21" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="21" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="21" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" s="21" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="B38" s="21" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B39" s="21" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B40" s="21" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B42" s="21" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="B44" s="21" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="B45" s="21" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B46" s="21" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="B47" s="21" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="B48" s="21" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B49" s="21" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="B50" s="21" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B51" s="21" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="B52" s="21" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="B53" s="21" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B54" s="21" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="B55" s="21" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="B56" s="21" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A57" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="B57" s="21" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A58" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="B58" s="21" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A59" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="B59" s="21" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A60" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="B60" s="21" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A61" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="B61" s="21" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A62" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="B62" s="21" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A63" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="B63" s="21" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B64" s="21" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B65" s="21" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="B66" s="21" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="B67" s="21" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="B68" s="21" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="B69" s="21" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="B70" s="21" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="B71" s="21" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="B72" s="21" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="B73" s="21" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="B74" s="21" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A75" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="B75" s="21" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A76" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="B76" s="21" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A77" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="B77" s="21" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A78" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B78" s="21" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A79" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="B79" s="21" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A80" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="B80" s="21" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A81" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B81" s="21" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A82" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="B82" s="21" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A83" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="B83" s="21" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A84" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="B84" s="21" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A85" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="B85" s="21" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A86" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="B86" s="21" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A87" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="B87" s="21" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A88" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="B88" s="21" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A89" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="B89" s="21" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A90" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="B90" s="21" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A91" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="B91" s="21" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A92" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="B92" s="21" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A93" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="B93" s="21" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A94" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="B94" s="21" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A95" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="B95" s="21" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A96" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B96" s="21" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A97" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="B97" s="21" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A98" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="B98" s="21" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A99" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="B99" s="21" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A100" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="B100" s="21" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A101" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="B101" s="21" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A102" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="B102" s="21" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A103" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="B103" s="21" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A104" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="B104" s="21" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A105" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="B105" s="21" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A106" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="B106" s="21" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A107" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="B107" s="21" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A108" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="B108" s="21" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A109" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="B109" s="21" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A110" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="B110" s="21" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A111" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B111" s="21" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A112" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="B112" s="21" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A113" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B113" s="21" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A114" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="B114" s="21" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A115" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="B115" s="21" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A116" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="B116" s="21" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A117" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="B117" s="21" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A118" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="B118" s="21" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A119" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="B119" s="21" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A120" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="B120" s="21" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A121" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="B121" s="21" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A122" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="B122" s="21" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A123" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="B123" s="21" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A124" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="B124" s="21" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A125" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="B125" s="21" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A126" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="B126" s="21" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A127" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B127" s="21" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A128" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="B128" s="21" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A129" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="B129" s="21" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A130" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="B130" s="21" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A131" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="B131" s="21" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A132" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="B132" s="21" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A133" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="B133" s="21" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A134" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="B134" s="21" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A135" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="B135" s="21" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A136" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="B136" s="21" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A137" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="B137" s="21" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A138" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="B138" s="21" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A139" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="B139" s="21" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A140" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="B140" s="21" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A141" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="B141" s="21" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A142" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="B142" s="21" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A143" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="B143" s="21" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A144" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="B144" s="21" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A145" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="B145" s="21" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A146" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="B146" s="21" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A147" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="B147" s="21" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A148" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="B148" s="21" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A149" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="B149" s="21" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A150" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="B150" s="21" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A151" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="B151" s="21" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A152" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="B152" s="21" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A153" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="B153" s="21" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A154" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="B154" s="21" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A155" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="B155" s="21" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A156" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="B156" s="21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A157" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="B157" s="21" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A158" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="B158" s="21" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A159" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="B159" s="21" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A160" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="B160" s="21" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A161" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="B161" s="21" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A162" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="B162" s="21" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A163" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="B163" s="21" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A164" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="B164" s="21" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A165" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="B165" s="21" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A166" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="B166" s="21" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A167" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="B167" s="21" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A168" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="B168" s="21" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A169" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="B169" s="21" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A170" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="B170" s="21" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A171" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="B171" s="21" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A172" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="B172" s="21" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A173" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="B173" s="21" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A174" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="B174" s="21" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A175" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="B175" s="21" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A176" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="B176" s="21" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A177" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="B177" s="21" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A178" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="B178" s="21" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A179" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="B179" s="21" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A180" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="B180" s="21" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A181" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="B181" s="21" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A182" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="B182" s="21" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A183" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="B183" s="21" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A184" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="B184" s="21" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A185" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="B185" s="21" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A186" s="21" t="s">
-        <v>205</v>
-      </c>
-      <c r="B186" s="21" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A187" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="B187" s="21" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A188" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="B188" s="21" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A189" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="B189" s="21" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A190" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="B190" s="21" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A191" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="B191" s="21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A192" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="B192" s="21" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A193" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="B193" s="21" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A194" s="21" t="s">
-        <v>213</v>
-      </c>
-      <c r="B194" s="21" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A195" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="B195" s="21" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A196" s="21" t="s">
-        <v>215</v>
-      </c>
-      <c r="B196" s="21" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A197" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="B197" s="21" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A198" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="B198" s="21" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A199" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="B199" s="21" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A200" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="B200" s="21" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A201" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="B201" s="21" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A202" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="B202" s="21" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A203" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="B203" s="21" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A204" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="B204" s="21" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A205" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="B205" s="21" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A206" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="B206" s="21" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A207" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="B207" s="21" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A208" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="B208" s="21" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A209" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="B209" s="21" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A210" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="B210" s="21" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A211" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="B211" s="21" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A212" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="B212" s="21" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A213" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="B213" s="21" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A214" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="B214" s="21" t="s">
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A217" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="B217" s="20" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A215" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="B215" s="21" t="s">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A218" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="B218" s="20" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A216" s="21" t="s">
-        <v>235</v>
-      </c>
-      <c r="B216" s="21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A217" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="B217" s="21" t="s">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A219" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="B219" s="20" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A220" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="B220" s="20" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A221" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="B221" s="20" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A218" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="B218" s="21" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A219" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="B219" s="21" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A220" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="B220" s="21" t="s">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A222" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="B222" s="20" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A221" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="B221" s="21" t="s">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A223" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="B223" s="20" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A224" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="B224" s="20" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A222" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="B222" s="21" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A223" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="B223" s="21" t="s">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A225" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="B225" s="20" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A226" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="B226" s="21" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A227" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="B227" s="21" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A228" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="B228" s="21" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A229" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="B229" s="21" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A230" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="B230" s="21" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A231" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="B231" s="21" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A232" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="B232" s="21" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A233" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="B233" s="21" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A234" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="B234" s="21" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A235" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="B235" s="21" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A236" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="B236" s="21" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A237" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="B237" s="21" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A238" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="B238" s="21" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A239" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="B239" s="21" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A240" s="20" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A224" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="B224" s="21" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A225" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="B225" s="21" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A226" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="B226" s="22" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A227" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="B227" s="22" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A228" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="B228" s="22" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A229" s="21" t="s">
-        <v>248</v>
-      </c>
-      <c r="B229" s="22" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A230" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="B230" s="22" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A231" s="21" t="s">
-        <v>250</v>
-      </c>
-      <c r="B231" s="22" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A232" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="B232" s="22" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A233" s="21" t="s">
-        <v>252</v>
-      </c>
-      <c r="B233" s="22" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A234" s="21" t="s">
-        <v>253</v>
-      </c>
-      <c r="B234" s="22" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A235" s="21" t="s">
-        <v>254</v>
-      </c>
-      <c r="B235" s="22" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A236" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="B236" s="22" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A237" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="B237" s="22" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A238" s="21" t="s">
-        <v>257</v>
-      </c>
-      <c r="B238" s="22" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A239" s="21" t="s">
-        <v>258</v>
-      </c>
-      <c r="B239" s="22" t="s">
+      <c r="B240" s="21" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A240" s="21" t="s">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A241" s="20" t="s">
         <v>480</v>
       </c>
-      <c r="B240" s="22" t="s">
+      <c r="B241" s="21" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A241" s="21" t="s">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A242" s="20" t="s">
         <v>481</v>
       </c>
-      <c r="B241" s="22" t="s">
+      <c r="B242" s="21" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A242" s="21" t="s">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A243" s="20" t="s">
         <v>482</v>
       </c>
-      <c r="B242" s="22" t="s">
+      <c r="B243" s="21" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A243" s="21" t="s">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A244" s="20" t="s">
         <v>483</v>
       </c>
-      <c r="B243" s="22" t="s">
+      <c r="B244" s="21" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A244" s="21" t="s">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A245" s="20" t="s">
         <v>484</v>
       </c>
-      <c r="B244" s="22" t="s">
+      <c r="B245" s="21" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A245" s="21" t="s">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A246" s="20" t="s">
         <v>485</v>
       </c>
-      <c r="B245" s="22" t="s">
+      <c r="B246" s="21" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A246" s="21" t="s">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A247" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="B246" s="22" t="s">
+      <c r="B247" s="21" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A247" s="21" t="s">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A248" s="20" t="s">
         <v>487</v>
       </c>
-      <c r="B247" s="22" t="s">
+      <c r="B248" s="21" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A248" s="21" t="s">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A249" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="B248" s="22" t="s">
+      <c r="B249" s="21" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A249" s="21" t="s">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A250" s="20" t="s">
         <v>489</v>
       </c>
-      <c r="B249" s="22" t="s">
+      <c r="B250" s="21" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A250" s="21" t="s">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A251" t="s">
         <v>490</v>
       </c>
-      <c r="B250" s="22" t="s">
+      <c r="B251" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A251" s="19" t="s">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A252" t="s">
         <v>491</v>
       </c>
-      <c r="B251" s="19" t="s">
+      <c r="B252" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A252" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="B252" s="19" t="s">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A253" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A253" s="19" t="s">
+      <c r="B253" t="s">
         <v>520</v>
       </c>
-      <c r="B253" s="19" t="s">
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A254" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A254" s="19" t="s">
+      <c r="B254" t="s">
         <v>522</v>
       </c>
-      <c r="B254" s="19" t="s">
-        <v>523</v>
-      </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A255" s="19" t="s">
+      <c r="A255" t="s">
+        <v>524</v>
+      </c>
+      <c r="B255" t="s">
         <v>525</v>
       </c>
-      <c r="B255" s="19" t="s">
-        <v>526</v>
-      </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A256" s="23"/>
+      <c r="A256" s="1"/>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A257" s="23"/>
+      <c r="A257" s="1"/>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A258" s="23"/>
+      <c r="A258" s="1"/>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A259" s="23"/>
+      <c r="A259" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/vo_new_terms_IDs.xlsx
+++ b/src/vo_new_terms_IDs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiezhen/Documents/Ontology/VO/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FD4CAA-3AF0-7F4F-B386-908C6F8984FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1060A5C0-7578-ED4C-89D0-F33D8F1DB081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6200" yWindow="2360" windowWidth="24200" windowHeight="13000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2560" yWindow="3640" windowWidth="24200" windowHeight="13000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VO IDs range" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="551">
   <si>
     <t>vaccine adjuvant</t>
   </si>
@@ -1626,9 +1626,6 @@
     <t>VO:0010504</t>
   </si>
   <si>
-    <t>Assign new ID for new VO classes</t>
-  </si>
-  <si>
     <t>Assign new ID for new VO annotation or object properties</t>
   </si>
   <si>
@@ -1651,6 +1648,45 @@
   </si>
   <si>
     <t>macrophage vaccine antigen processing and presentation</t>
+  </si>
+  <si>
+    <t>VO:0010507</t>
+  </si>
+  <si>
+    <t>VO:0010508</t>
+  </si>
+  <si>
+    <t>VO:0010509</t>
+  </si>
+  <si>
+    <t>VO:0010510</t>
+  </si>
+  <si>
+    <t>VO:0010511</t>
+  </si>
+  <si>
+    <t>VO:0010512</t>
+  </si>
+  <si>
+    <t>VO:0010513</t>
+  </si>
+  <si>
+    <t>VO:0010514</t>
+  </si>
+  <si>
+    <t>VO:0010515</t>
+  </si>
+  <si>
+    <t>Assign new ID for new VO classes/instances</t>
+  </si>
+  <si>
+    <t>CAPVAXIVE</t>
+  </si>
+  <si>
+    <t>capsular polysaccharide vaccine role</t>
+  </si>
+  <si>
+    <t>polysaccharide vaccine role</t>
   </si>
 </sst>
 </file>
@@ -2301,10 +2337,8 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="45">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2730,22 +2764,22 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>530</v>
+        <v>547</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -2984,7 +3018,9 @@
   <cols>
     <col min="1" max="1" width="20.33203125" customWidth="1"/>
     <col min="2" max="2" width="30.1640625" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="52.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -2995,7 +3031,7 @@
         <v>528</v>
       </c>
       <c r="H1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -3011,7 +3047,7 @@
       <c r="F2" t="s">
         <v>527</v>
       </c>
-      <c r="H2" s="23"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="20" t="s">
@@ -3023,8 +3059,8 @@
       <c r="E3" t="s">
         <v>529</v>
       </c>
-      <c r="F3" s="24" t="s">
-        <v>534</v>
+      <c r="F3" s="23" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -3035,10 +3071,10 @@
         <v>259</v>
       </c>
       <c r="E4" t="s">
+        <v>534</v>
+      </c>
+      <c r="F4" s="23" t="s">
         <v>535</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -3049,10 +3085,10 @@
         <v>260</v>
       </c>
       <c r="E5" t="s">
+        <v>536</v>
+      </c>
+      <c r="F5" s="23" t="s">
         <v>537</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -3062,6 +3098,15 @@
       <c r="B6" s="20" t="s">
         <v>470</v>
       </c>
+      <c r="D6" s="24">
+        <v>46184</v>
+      </c>
+      <c r="E6" t="s">
+        <v>538</v>
+      </c>
+      <c r="F6" t="s">
+        <v>550</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
@@ -3070,6 +3115,15 @@
       <c r="B7" s="20" t="s">
         <v>261</v>
       </c>
+      <c r="D7" s="24">
+        <v>46184</v>
+      </c>
+      <c r="E7" t="s">
+        <v>539</v>
+      </c>
+      <c r="F7" t="s">
+        <v>549</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
@@ -3078,6 +3132,15 @@
       <c r="B8" s="20" t="s">
         <v>262</v>
       </c>
+      <c r="D8" s="24">
+        <v>46184</v>
+      </c>
+      <c r="E8" t="s">
+        <v>540</v>
+      </c>
+      <c r="F8" t="s">
+        <v>548</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
@@ -3086,6 +3149,9 @@
       <c r="B9" s="20" t="s">
         <v>263</v>
       </c>
+      <c r="E9" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
@@ -3094,6 +3160,9 @@
       <c r="B10" s="20" t="s">
         <v>264</v>
       </c>
+      <c r="E10" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
@@ -3102,6 +3171,9 @@
       <c r="B11" s="20" t="s">
         <v>265</v>
       </c>
+      <c r="E11" t="s">
+        <v>543</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
@@ -3110,6 +3182,9 @@
       <c r="B12" s="20" t="s">
         <v>266</v>
       </c>
+      <c r="E12" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="20" t="s">
@@ -3118,6 +3193,9 @@
       <c r="B13" s="20" t="s">
         <v>267</v>
       </c>
+      <c r="E13" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
@@ -3126,6 +3204,9 @@
       <c r="B14" s="20" t="s">
         <v>268</v>
       </c>
+      <c r="E14" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="19" t="s">
@@ -5068,6 +5149,7 @@
       <c r="A259" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/vo_new_terms_IDs.xlsx
+++ b/src/vo_new_terms_IDs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiezhen/Documents/Ontology/VO/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1060A5C0-7578-ED4C-89D0-F33D8F1DB081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3344D0B3-238F-EF40-9019-2FC57EC901C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2560" yWindow="3640" windowWidth="24200" windowHeight="13000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6040" yWindow="800" windowWidth="24200" windowHeight="13000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VO IDs range" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="556">
   <si>
     <t>vaccine adjuvant</t>
   </si>
@@ -1687,6 +1687,21 @@
   </si>
   <si>
     <t>polysaccharide vaccine role</t>
+  </si>
+  <si>
+    <t>lipopolysaccharide vaccine role</t>
+  </si>
+  <si>
+    <t>Streptococcus pneumoniae DNA vaccine</t>
+  </si>
+  <si>
+    <t>Streptococcus pneumoniae conjugate vaccine</t>
+  </si>
+  <si>
+    <t>Streptococcus pneumoniae recombinant vector vaccine</t>
+  </si>
+  <si>
+    <t>Streptococcus pneumoniae subunit vaccine</t>
   </si>
 </sst>
 </file>
@@ -2307,7 +2322,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2337,7 +2352,6 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="45">
@@ -2769,7 +2783,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
@@ -3059,7 +3073,7 @@
       <c r="E3" t="s">
         <v>529</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" t="s">
         <v>533</v>
       </c>
     </row>
@@ -3073,7 +3087,7 @@
       <c r="E4" t="s">
         <v>534</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" t="s">
         <v>535</v>
       </c>
     </row>
@@ -3087,7 +3101,7 @@
       <c r="E5" t="s">
         <v>536</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" t="s">
         <v>537</v>
       </c>
     </row>
@@ -3098,7 +3112,7 @@
       <c r="B6" s="20" t="s">
         <v>470</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="23">
         <v>46184</v>
       </c>
       <c r="E6" t="s">
@@ -3115,7 +3129,7 @@
       <c r="B7" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="23">
         <v>46184</v>
       </c>
       <c r="E7" t="s">
@@ -3132,7 +3146,7 @@
       <c r="B8" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="23">
         <v>46184</v>
       </c>
       <c r="E8" t="s">
@@ -3149,8 +3163,14 @@
       <c r="B9" s="20" t="s">
         <v>263</v>
       </c>
+      <c r="D9" s="23">
+        <v>46184</v>
+      </c>
       <c r="E9" t="s">
         <v>541</v>
+      </c>
+      <c r="F9" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -3160,8 +3180,14 @@
       <c r="B10" s="20" t="s">
         <v>264</v>
       </c>
+      <c r="D10" s="23">
+        <v>46184</v>
+      </c>
       <c r="E10" t="s">
         <v>542</v>
+      </c>
+      <c r="F10" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -3171,8 +3197,14 @@
       <c r="B11" s="20" t="s">
         <v>265</v>
       </c>
+      <c r="D11" s="23">
+        <v>46184</v>
+      </c>
       <c r="E11" t="s">
         <v>543</v>
+      </c>
+      <c r="F11" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -3182,8 +3214,14 @@
       <c r="B12" s="20" t="s">
         <v>266</v>
       </c>
+      <c r="D12" s="23">
+        <v>46184</v>
+      </c>
       <c r="E12" t="s">
         <v>544</v>
+      </c>
+      <c r="F12" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -3193,8 +3231,14 @@
       <c r="B13" s="20" t="s">
         <v>267</v>
       </c>
+      <c r="D13" s="23">
+        <v>46184</v>
+      </c>
       <c r="E13" t="s">
         <v>545</v>
+      </c>
+      <c r="F13" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -5151,5 +5195,6 @@
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>